--- a/artfynd/A 61384-2021 artfynd.xlsx
+++ b/artfynd/A 61384-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61384-2021 artfynd.xlsx
+++ b/artfynd/A 61384-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>88678586</v>
       </c>
       <c r="B2" t="n">
-        <v>85187</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578403.2894104348</v>
+        <v>578403</v>
       </c>
       <c r="R2" t="n">
-        <v>6540266.539617862</v>
+        <v>6540267</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -751,19 +746,9 @@
           <t>2020-10-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93099394</v>
+        <v>93099393</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578308.0527989249</v>
+        <v>578320</v>
       </c>
       <c r="R3" t="n">
-        <v>6540303.251660425</v>
+        <v>6540291</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2021-04-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93099395</v>
+        <v>93099394</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578308.0738102532</v>
+        <v>578308</v>
       </c>
       <c r="R4" t="n">
-        <v>6540302.221287026</v>
+        <v>6540304</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +950,9 @@
           <t>2021-04-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93099393</v>
+        <v>93099395</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578320.1859624664</v>
+        <v>578308</v>
       </c>
       <c r="R5" t="n">
-        <v>6540290.61405436</v>
+        <v>6540303</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1051,9 @@
           <t>2021-04-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,12 +1087,7 @@
         <v>93099396</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578308.1578556027</v>
+        <v>578308</v>
       </c>
       <c r="R6" t="n">
-        <v>6540298.099790676</v>
+        <v>6540298</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,19 +1152,9 @@
           <t>2021-04-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61384-2021 artfynd.xlsx
+++ b/artfynd/A 61384-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88678586</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93099393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93099394</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93099395</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93099396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>